--- a/RESULTS/tables/missingness_indicator_development.xlsx
+++ b/RESULTS/tables/missingness_indicator_development.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Missing N</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Missing Percent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Missing Percent Dead</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Missing Percent Alive</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Difference Dead-Alive</t>
         </is>
@@ -485,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>結案日期</t>
+          <t>入家日期</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -507,7 +495,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>意識分級</t>
+          <t>結案日期</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -529,7 +517,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>入家日期</t>
+          <t>意識分級</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -551,7 +539,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>disease_last_score</t>
+          <t>disease_diff_seq</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -573,7 +561,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>disease_diff_seq</t>
+          <t>disease_last_score</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -617,7 +605,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>disease_Max</t>
+          <t>disease_Min</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -639,7 +627,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>disease_Min</t>
+          <t>disease_Max</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -683,7 +671,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>last_ 意識_V</t>
+          <t>first_ 意識_V</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -705,7 +693,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>first_ 意識_V</t>
+          <t>last_ 意識_V</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -727,7 +715,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>last_ 意識_E</t>
+          <t>first_ 意識_E</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -749,7 +737,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>first_ 意識_E</t>
+          <t>last_ 意識_E</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -771,7 +759,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>first_ 意識_M</t>
+          <t>last_ 意識_M</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -793,7 +781,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>last_ 意識_M</t>
+          <t>first_ 意識_M</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -815,7 +803,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ADL_std</t>
+          <t>ADL_last_score</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -859,7 +847,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ADL_last_score</t>
+          <t>ADL_std</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -881,7 +869,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BW_diff_seq</t>
+          <t>BW_last</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -903,7 +891,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BW_last</t>
+          <t>BW_diff_seq</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -947,7 +935,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>使用呼吸輔具</t>
+          <t>diff_has_feeding_tube</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -969,7 +957,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>had_fall</t>
+          <t>意識總分_diff</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -991,7 +979,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>diff_has_feeding_tube</t>
+          <t>last_has_denture</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1013,7 +1001,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>last_has_feeding_tube</t>
+          <t>first_has_denture</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1035,7 +1023,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>first_has_feeding_tube</t>
+          <t>意識總分Max</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1057,7 +1045,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>last_ 意識總分</t>
+          <t>diff_has_denture</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1079,7 +1067,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>意識總分_diff</t>
+          <t>first_ 意識總分</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1101,7 +1089,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>意識總分Max</t>
+          <t>first_has_feeding_tube</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1123,7 +1111,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>first_has_denture</t>
+          <t>last_has_feeding_tube</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1145,7 +1133,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>first_ 意識總分</t>
+          <t>last_ 意識總分</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1167,7 +1155,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>diff_has_denture</t>
+          <t>使用呼吸輔具</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1189,7 +1177,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>last_has_denture</t>
+          <t>had_fall</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1233,7 +1221,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ADL_Max</t>
+          <t>ADL_Min</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1255,7 +1243,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ADL_Min</t>
+          <t>ADL_Max</t>
         </is>
       </c>
       <c r="B38" t="n">
